--- a/converted_files/837/837P-minimal.xlsx
+++ b/converted_files/837/837P-minimal.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05825</t>
+          <t>6a04cb3c618f76c4f7b196d6</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/837/837P-minimal.xlsx
+++ b/converted_files/837/837P-minimal.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b196d6</t>
+          <t>6a04cc5c1ef26d534baf41e4</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/837/837P-minimal.xlsx
+++ b/converted_files/837/837P-minimal.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf41e4</t>
+          <t>6a0614dff8d6a2fc7434902e</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/837/837P-minimal.xlsx
+++ b/converted_files/837/837P-minimal.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc7434902e</t>
+          <t>6a32cb6597613a0e49909709</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
